--- a/Result/profitability/2231.xlsx
+++ b/Result/profitability/2231.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.53</v>
       </c>
       <c r="M2" t="n">
-        <v>0.20125</v>
+        <v>0.125</v>
       </c>
       <c r="N2" t="n">
-        <v>33.88</v>
+        <v>33.91875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.66</v>
       </c>
       <c r="M3" t="n">
-        <v>0.20875</v>
+        <v>-0.007500000000000007</v>
       </c>
       <c r="N3" t="n">
-        <v>33.9525</v>
+        <v>34.42375000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.12625</v>
+        <v>0.03750000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>34.7375</v>
+        <v>33.90625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -914,13 +914,13 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.75</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1325</v>
+        <v>0.2625</v>
       </c>
       <c r="N5" t="n">
-        <v>34.04</v>
+        <v>34.0325</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.93</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3800000000000001</v>
+        <v>0.34375</v>
       </c>
       <c r="N6" t="n">
-        <v>34.79375</v>
+        <v>35.19625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4325</v>
+        <v>0.6275000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>35.87375</v>
+        <v>37.30375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0.81625</v>
+        <v>0.765</v>
       </c>
       <c r="N8" t="n">
-        <v>38.6075</v>
+        <v>38.405</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1521,7 +1521,7 @@
         <v>0.9375</v>
       </c>
       <c r="N9" t="n">
-        <v>39.48999999999999</v>
+        <v>39.49</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2231</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>727</v>
+      </c>
+      <c r="D75" t="n">
+        <v>472</v>
+      </c>
+      <c r="E75" t="n">
+        <v>255</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.59%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.13375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.78875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.025</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.619999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04412966494143278</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9904761904761905</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.05999999999999517</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.001706970128022567</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
